--- a/Shiny/Datos limpios/pricing_semanal_historico_trigo.xlsx
+++ b/Shiny/Datos limpios/pricing_semanal_historico_trigo.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M572"/>
+  <dimension ref="A1:M575"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="20.7109375" style="2" customWidth="1"/>
@@ -24648,16 +24648,16 @@
         <v>45908</v>
       </c>
       <c r="D565">
-        <v>323695.9</v>
+        <v>323095.9</v>
       </c>
       <c r="E565">
-        <v>4673.79</v>
+        <v>5133.11</v>
       </c>
       <c r="F565">
         <v>6880.69</v>
       </c>
       <c r="G565">
-        <v>321489</v>
+        <v>321348.32</v>
       </c>
       <c r="H565">
         <v>46351.94</v>
@@ -24672,7 +24672,7 @@
         <v>46866.97</v>
       </c>
       <c r="L565">
-        <v>368355.97</v>
+        <v>368215.29</v>
       </c>
       <c r="M565" t="inlineStr">
         <is>
@@ -24691,16 +24691,16 @@
         <v>45915</v>
       </c>
       <c r="D566">
-        <v>435871.18</v>
+        <v>435775.18</v>
       </c>
       <c r="E566">
-        <v>7163.66</v>
+        <v>7225.74</v>
       </c>
       <c r="F566">
         <v>3010.61</v>
       </c>
       <c r="G566">
-        <v>440024.23</v>
+        <v>439990.31</v>
       </c>
       <c r="H566">
         <v>81801.16</v>
@@ -24715,7 +24715,7 @@
         <v>80867.02</v>
       </c>
       <c r="L566">
-        <v>520891.25</v>
+        <v>520857.33</v>
       </c>
       <c r="M566" t="inlineStr">
         <is>
@@ -24734,16 +24734,16 @@
         <v>45922</v>
       </c>
       <c r="D567">
-        <v>541014.75</v>
+        <v>539514.75</v>
       </c>
       <c r="E567">
-        <v>13320.09</v>
+        <v>14132.36</v>
       </c>
       <c r="F567">
-        <v>11319.14</v>
+        <v>11819.14</v>
       </c>
       <c r="G567">
-        <v>543015.7</v>
+        <v>541827.97</v>
       </c>
       <c r="H567">
         <v>51071.5</v>
@@ -24758,7 +24758,7 @@
         <v>51158.44</v>
       </c>
       <c r="L567">
-        <v>594174.1399999999</v>
+        <v>592986.4099999999</v>
       </c>
       <c r="M567" t="inlineStr">
         <is>
@@ -24777,16 +24777,16 @@
         <v>45929</v>
       </c>
       <c r="D568">
-        <v>289002.63</v>
+        <v>284002.63</v>
       </c>
       <c r="E568">
-        <v>7354.99</v>
+        <v>11943.41</v>
       </c>
       <c r="F568">
         <v>1445.36</v>
       </c>
       <c r="G568">
-        <v>294912.26</v>
+        <v>294500.68</v>
       </c>
       <c r="H568">
         <v>40522.82</v>
@@ -24801,7 +24801,7 @@
         <v>40671.28</v>
       </c>
       <c r="L568">
-        <v>335583.54</v>
+        <v>335171.96</v>
       </c>
       <c r="M568" t="inlineStr">
         <is>
@@ -24820,16 +24820,16 @@
         <v>45936</v>
       </c>
       <c r="D569">
-        <v>457425.66</v>
+        <v>457225.66</v>
       </c>
       <c r="E569">
-        <v>6785.51</v>
+        <v>6830.24</v>
       </c>
       <c r="F569">
         <v>7315.38</v>
       </c>
       <c r="G569">
-        <v>456895.79</v>
+        <v>456740.52</v>
       </c>
       <c r="H569">
         <v>32757.28</v>
@@ -24844,7 +24844,7 @@
         <v>32757.28</v>
       </c>
       <c r="L569">
-        <v>489653.0699999999</v>
+        <v>489497.7999999999</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
@@ -24863,16 +24863,16 @@
         <v>45943</v>
       </c>
       <c r="D570">
-        <v>731154.48</v>
+        <v>729154.48</v>
       </c>
       <c r="E570">
-        <v>16717.91</v>
+        <v>18421.35</v>
       </c>
       <c r="F570">
         <v>4268.77</v>
       </c>
       <c r="G570">
-        <v>743603.62</v>
+        <v>743307.0599999999</v>
       </c>
       <c r="H570">
         <v>29893.04</v>
@@ -24887,7 +24887,7 @@
         <v>29993.04</v>
       </c>
       <c r="L570">
-        <v>773596.66</v>
+        <v>773300.1</v>
       </c>
       <c r="M570" t="inlineStr">
         <is>
@@ -24949,33 +24949,162 @@
         <v>45957</v>
       </c>
       <c r="D572">
-        <v>960</v>
+        <v>358767.99</v>
       </c>
       <c r="E572">
-        <v>0</v>
+        <v>5365.76</v>
       </c>
       <c r="F572">
-        <v>0</v>
+        <v>5767.29</v>
       </c>
       <c r="G572">
-        <v>960</v>
+        <v>358366.46</v>
       </c>
       <c r="H572">
-        <v>0</v>
+        <v>43197.87</v>
       </c>
       <c r="I572">
-        <v>0</v>
+        <v>404.46</v>
       </c>
       <c r="J572">
-        <v>0</v>
+        <v>2136.56</v>
       </c>
       <c r="K572">
-        <v>0</v>
+        <v>41465.77</v>
       </c>
       <c r="L572">
-        <v>960</v>
+        <v>399832.23</v>
       </c>
       <c r="M572" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573">
+        <v>2025</v>
+      </c>
+      <c r="B573">
+        <v>45</v>
+      </c>
+      <c r="C573" s="2">
+        <v>45964</v>
+      </c>
+      <c r="D573">
+        <v>359071.7</v>
+      </c>
+      <c r="E573">
+        <v>10102.47</v>
+      </c>
+      <c r="F573">
+        <v>6143.87</v>
+      </c>
+      <c r="G573">
+        <v>363030.3</v>
+      </c>
+      <c r="H573">
+        <v>42976.97</v>
+      </c>
+      <c r="I573">
+        <v>0</v>
+      </c>
+      <c r="J573">
+        <v>480</v>
+      </c>
+      <c r="K573">
+        <v>42496.97</v>
+      </c>
+      <c r="L573">
+        <v>405527.27</v>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574">
+        <v>2025</v>
+      </c>
+      <c r="B574">
+        <v>46</v>
+      </c>
+      <c r="C574" s="2">
+        <v>45971</v>
+      </c>
+      <c r="D574">
+        <v>542530.45</v>
+      </c>
+      <c r="E574">
+        <v>3178.69</v>
+      </c>
+      <c r="F574">
+        <v>7871.59</v>
+      </c>
+      <c r="G574">
+        <v>537837.5499999999</v>
+      </c>
+      <c r="H574">
+        <v>62725.96</v>
+      </c>
+      <c r="I574">
+        <v>388.53</v>
+      </c>
+      <c r="J574">
+        <v>0</v>
+      </c>
+      <c r="K574">
+        <v>63114.49</v>
+      </c>
+      <c r="L574">
+        <v>600952.0399999999</v>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>TRIGO</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575">
+        <v>2025</v>
+      </c>
+      <c r="B575">
+        <v>47</v>
+      </c>
+      <c r="C575" s="2">
+        <v>45978</v>
+      </c>
+      <c r="D575">
+        <v>449503.07</v>
+      </c>
+      <c r="E575">
+        <v>6098.1</v>
+      </c>
+      <c r="F575">
+        <v>7454</v>
+      </c>
+      <c r="G575">
+        <v>448147.17</v>
+      </c>
+      <c r="H575">
+        <v>39276.31</v>
+      </c>
+      <c r="I575">
+        <v>249.67</v>
+      </c>
+      <c r="J575">
+        <v>330</v>
+      </c>
+      <c r="K575">
+        <v>39195.98</v>
+      </c>
+      <c r="L575">
+        <v>487343.15</v>
+      </c>
+      <c r="M575" t="inlineStr">
         <is>
           <t>TRIGO</t>
         </is>
